--- a/task170/golden/c7_tld_order.xlsx
+++ b/task170/golden/c7_tld_order.xlsx
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
-  <si>
-    <t>C7 order of TLD 30s: 2,690,000 bottles</t>
-  </si>
-  <si>
-    <t>TDF/3TC/DTG 300/300/50 mg tablets, bottle of 30 (ARV0412), for January to June 2027. Stock count of 31 August 2026; SOP QP-04 version 3, sections 3 and 4; September 2026 quantification review.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
+  <si>
+    <t>C7 order of TLD 30s: line 1, 342 pallets; line 2, 11 pallets</t>
+  </si>
+  <si>
+    <t>TDF/3TC/DTG 300/300/50 mg tablets, bottle of 30 (ARV0412), for January to June 2027. Stock count of 31 August 2026; SOP QP-04 version 3, sections 3 and 4; pallets of 84 cartons of 96 bottles (8,064 bottles); September 2026 quantification review.</t>
   </si>
   <si>
     <t>Line</t>
@@ -40,31 +40,34 @@
     <t>Bottles</t>
   </si>
   <si>
-    <t>Patients aged 15 and over at the count or starting after it: consumption, September 2026 to June 2027 (programme projection)</t>
-  </si>
-  <si>
-    <t>Patients aged 15 and over at the count or starting after it: maximum stock, six months of June 2027</t>
-  </si>
-  <si>
-    <t>Children under 15 at the count: consumption, September 2026 to June 2027 (paediatric register forecast)</t>
-  </si>
-  <si>
-    <t>Children under 15 at the count: maximum stock, six months of June 2027</t>
-  </si>
-  <si>
-    <t>Forecast need</t>
-  </si>
-  <si>
-    <t>Less usable stock at the count, Main warehouse and Northern depot</t>
-  </si>
-  <si>
-    <t>Less confirmed shipments due by 30 June 2027 (PO-2026-0147, lots 1 to 3)</t>
-  </si>
-  <si>
-    <t>Order before rounding</t>
-  </si>
-  <si>
-    <t>C7 order, nearest 5,000 bottles</t>
+    <t>Line 1. Patients aged 15 and over at the count or starting after it: consumption, September 2026 to June 2027 (programme projection)</t>
+  </si>
+  <si>
+    <t>Line 1. Maximum stock, six months of June 2027</t>
+  </si>
+  <si>
+    <t>Line 1. Less usable stock at the count, Main warehouse and Northern depot</t>
+  </si>
+  <si>
+    <t>Line 1. Less confirmed shipments due by 30 June 2027 (PO-2026-0147, lots 1 to 3)</t>
+  </si>
+  <si>
+    <t>Line 1 before rounding</t>
+  </si>
+  <si>
+    <t>Line 1, 342 pallets</t>
+  </si>
+  <si>
+    <t>Line 2. Children under 15 at the count: consumption, September 2026 to June 2027 (paediatric register forecast)</t>
+  </si>
+  <si>
+    <t>Line 2. Maximum stock, six months of June 2027</t>
+  </si>
+  <si>
+    <t>Line 2 before rounding</t>
+  </si>
+  <si>
+    <t>Line 2, 11 pallets</t>
   </si>
   <si>
     <t>Children under 15 on TLD at the count</t>
@@ -118,7 +121,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Expected children in care on TLD at each month's end, one bottle each (SOP 4.1). Children on TLD at the count are carried at the register's exit rates of the last 12 months, under 12 and 12 and over. Each child on a paediatric first-line regimen: a straight line through every weighing since January 2023; each scheduled visit to June 2027, at the child's months-dispensed interval from the next appointment, is weighed at the share of clinical visits of the last 12 months and the reading scatters around the line (residual SD 1.28 kg); the child moves onto TLD at the first reading of 30.0 kg or more (Annex 7.2).</t>
+    <t>Expected children in care on TLD at each month's end, one bottle each (SOP 4.1). Children on TLD at the count are carried at the register's exit rates of the last 12 months, under 12 and 12 and over. Each child on a paediatric first-line regimen: a straight line through every weighing since January 2023; each scheduled visit to June 2027, at the child's months-dispensed interval from the next appointment, is weighed at the share of clinical visits of the last 12 months and the reading scatters around the line (residual SD 1.29 kg); the child moves onto TLD at the first reading of 30.0 kg or more (Annex 7, 2026 edition), or, for the 9.5% of such readings since 1 March 2026 the clinician held back, at the next weighed visit.</t>
   </si>
   <si>
     <t>Forecast from</t>
@@ -127,6 +130,9 @@
     <t>Months</t>
   </si>
   <si>
+    <t>TLD from</t>
+  </si>
+  <si>
     <t>Bottle-months the register shows</t>
   </si>
   <si>
@@ -136,22 +142,22 @@
     <t>Error</t>
   </si>
   <si>
-    <t>Each line reaching 30 kg</t>
-  </si>
-  <si>
-    <t>Switch rates by recorded weight band</t>
+    <t>Each line reaching the band</t>
+  </si>
+  <si>
+    <t>31 Aug 2024</t>
+  </si>
+  <si>
+    <t>35 kg</t>
+  </si>
+  <si>
+    <t>28 Feb 2025</t>
   </si>
   <si>
     <t>31 Aug 2025</t>
   </si>
   <si>
-    <t>31 Dec 2025</t>
-  </si>
-  <si>
-    <t>28 Feb 2026</t>
-  </si>
-  <si>
-    <t>Each route stood at a month end the register has closed: the children in care on a paediatric first line at that date and their weighings to it, followed over the months shown; the register's later rows give the bottle-months they took on TLD.</t>
+    <t>Each forecast stood at a month end the register has closed, under the band then in force (TLD from 35 kg until the 2026 guidelines): the children in care on a paediatric first line at that date and their weighings to it, followed over the months shown; the register's later rows give the bottle-months they took on TLD.</t>
   </si>
   <si>
     <t>Region</t>
@@ -202,13 +208,13 @@
     <t>Prepared for</t>
   </si>
   <si>
-    <t>Quantification review, September 2026: the C7 order of TLD 30s</t>
+    <t>Quantification review, September 2026: the C7 order of TLD 30s, lines 1 and 2 (SOP 4.3)</t>
   </si>
   <si>
     <t>Stock count</t>
   </si>
   <si>
-    <t>31 August 2026, Main warehouse and Northern depot (SOP 2.1); the quarantined batch is not usable stock (SOP 3.3)</t>
+    <t>31 August 2026, Main warehouse and Northern depot (SOP 2.1); the quarantined batch is not usable stock (SOP 3.3); stock and shipments netted on line 1 alone (SOP 4.3)</t>
   </si>
   <si>
     <t>On order</t>
@@ -217,13 +223,13 @@
     <t>Lots with a supplier-confirmed delivery date on or before 30 June 2027; the C7 framework call-off FW-2027-C7A is planned and not on order (SOP 3.3)</t>
   </si>
   <si>
-    <t>Patients 15 and over</t>
+    <t>Line 1</t>
   </si>
   <si>
     <t>Programme projection, September 2026 round: patients aged 15 and over on 31 August 2026 and every patient starting treatment from 1 September 2026 (SOP 4.2)</t>
   </si>
   <si>
-    <t>Children under 15</t>
+    <t>Line 2</t>
   </si>
   <si>
     <t>Paediatric and adolescent ART register extract of 2 September 2026: children under 15 at the count with no outcome entered, forecast to 30 June 2027 whatever their age by then (SOP 4.2); the legacy layout linked through the 2024 crosswalk</t>
@@ -232,7 +238,7 @@
     <t>Rounding</t>
   </si>
   <si>
-    <t>Every line in whole bottles; the order rounded once to the nearest 5,000 bottles</t>
+    <t>Each line rounded once to the nearest whole pallet of 8,064 bottles (SOP 4.4); every other figure in whole bottles</t>
   </si>
 </sst>
 </file>
@@ -301,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -313,8 +319,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -621,10 +628,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBD79AC-3437-5563-9CB0-FDB66F273DBF}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="84.7109375" customWidth="1"/>
+    <col min="1" max="1" width="86.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -652,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>3142937</v>
+        <v>3138377</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>1908822</v>
+        <v>1903818</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -668,7 +675,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>48677</v>
+        <v>-1159770</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -676,23 +683,23 @@
         <v>7</v>
       </c>
       <c r="B8" s="5">
-        <v>38184</v>
+        <v>-1124544</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
-        <v>5138620</v>
+      <c r="B9" s="7">
+        <v>2757881</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
-        <v>-1376018</v>
+      <c r="B10" s="7">
+        <v>2757888</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -700,15 +707,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>-1072992</v>
+        <v>52710</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5">
-        <v>2689610</v>
+        <v>35274</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -716,15 +723,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="7">
-        <v>2690000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+        <v>87984</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="8">
-        <v>3348</v>
+      <c r="B14" s="7">
+        <v>88704</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -732,7 +739,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="8">
-        <v>12232</v>
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8">
+        <v>7151</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5525947-0DF7-5C90-AB06-9ABEEFED0044}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -756,169 +771,169 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="8">
-        <v>3334</v>
+        <v>4516</v>
       </c>
       <c r="C2" s="8">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="D2" s="8">
-        <v>3562</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="8">
-        <v>3319</v>
+        <v>4504</v>
       </c>
       <c r="C3" s="8">
-        <v>477</v>
+        <v>288</v>
       </c>
       <c r="D3" s="8">
-        <v>3796</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="8">
-        <v>3305</v>
+        <v>4493</v>
       </c>
       <c r="C4" s="8">
-        <v>749</v>
+        <v>433</v>
       </c>
       <c r="D4" s="8">
-        <v>4054</v>
+        <v>4926</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="8">
-        <v>3291</v>
+        <v>4481</v>
       </c>
       <c r="C5" s="8">
-        <v>1050</v>
+        <v>584</v>
       </c>
       <c r="D5" s="8">
-        <v>4341</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="8">
-        <v>3277</v>
+        <v>4469</v>
       </c>
       <c r="C6" s="8">
-        <v>1368</v>
+        <v>738</v>
       </c>
       <c r="D6" s="8">
-        <v>4645</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="8">
-        <v>3263</v>
+        <v>4458</v>
       </c>
       <c r="C7" s="8">
-        <v>1705</v>
+        <v>885</v>
       </c>
       <c r="D7" s="8">
-        <v>4968</v>
+        <v>5343</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="8">
-        <v>3248</v>
+        <v>4446</v>
       </c>
       <c r="C8" s="8">
-        <v>2052</v>
+        <v>1031</v>
       </c>
       <c r="D8" s="8">
-        <v>5300</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8">
-        <v>3234</v>
+        <v>4435</v>
       </c>
       <c r="C9" s="8">
-        <v>2414</v>
+        <v>1181</v>
       </c>
       <c r="D9" s="8">
-        <v>5648</v>
+        <v>5616</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="8">
-        <v>3220</v>
+        <v>4423</v>
       </c>
       <c r="C10" s="8">
-        <v>2779</v>
+        <v>1321</v>
       </c>
       <c r="D10" s="8">
-        <v>5999</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8">
-        <v>3206</v>
+        <v>4411</v>
       </c>
       <c r="C11" s="8">
-        <v>3158</v>
+        <v>1468</v>
       </c>
       <c r="D11" s="8">
-        <v>6364</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="7">
-        <v>48677</v>
+        <v>30</v>
+      </c>
+      <c r="D12" s="9">
+        <v>52710</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>30</v>
+      <c r="A14" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25"/>
@@ -926,9 +941,10 @@
     <row r="17" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:D19"/>
+    <mergeCell ref="A14:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -936,146 +952,134 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA74BA3-772A-5126-8B58-AB58F8D29504}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>12</v>
       </c>
-      <c r="C2" s="8">
-        <v>8198</v>
+      <c r="C2" t="s">
+        <v>40</v>
       </c>
       <c r="D2" s="8">
-        <v>8335</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0.01666728938803598</v>
-      </c>
-      <c r="F2" s="8">
-        <v>2375</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.7102616882232806</v>
-      </c>
-      <c r="H2" s="8">
-        <v>11594</v>
-      </c>
-      <c r="I2" s="10">
-        <v>0.4142262335275343</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4428</v>
+      </c>
+      <c r="E2" s="8">
+        <v>4079</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-0.07873456692698388</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2129</v>
+      </c>
+      <c r="H2" s="11">
+        <v>-0.5192064039893292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2481</v>
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
       </c>
       <c r="D3" s="8">
-        <v>2451</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-0.01228843036408585</v>
-      </c>
-      <c r="F3" s="8">
-        <v>310</v>
-      </c>
-      <c r="G3" s="10">
-        <v>-0.8751419156006063</v>
-      </c>
-      <c r="H3" s="8">
-        <v>3556</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0.4333114479923339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4721</v>
+      </c>
+      <c r="E3" s="8">
+        <v>4312</v>
+      </c>
+      <c r="F3" s="11">
+        <v>-0.08671767031424614</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2156</v>
+      </c>
+      <c r="H3" s="11">
+        <v>-0.5433063904477009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" s="8">
-        <v>3165</v>
+      <c r="C4" t="s">
+        <v>40</v>
       </c>
       <c r="D4" s="8">
-        <v>3077</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-0.02773811779175932</v>
-      </c>
-      <c r="F4" s="8">
-        <v>366</v>
-      </c>
-      <c r="G4" s="10">
-        <v>-0.8842520608707485</v>
-      </c>
-      <c r="H4" s="8">
-        <v>3988</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0.2601699193784461</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25"/>
+        <v>1279</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1113</v>
+      </c>
+      <c r="F4" s="11">
+        <v>-0.1300281037338202</v>
+      </c>
+      <c r="G4" s="8">
+        <v>344</v>
+      </c>
+      <c r="H4" s="11">
+        <v>-0.73091656085319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:I8"/>
+    <mergeCell ref="A6:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1095,143 +1099,143 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="8">
-        <v>329436</v>
+        <v>332616</v>
       </c>
       <c r="C2" s="8">
-        <v>317316</v>
+        <v>313068</v>
       </c>
       <c r="D2" s="8">
-        <v>336471</v>
+        <v>328751</v>
       </c>
       <c r="E2" s="8">
-        <v>336512</v>
+        <v>329253</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="8">
-        <v>364920</v>
+        <v>386916</v>
       </c>
       <c r="C3" s="8">
-        <v>348504</v>
+        <v>373512</v>
       </c>
       <c r="D3" s="8">
-        <v>362261</v>
+        <v>382391</v>
       </c>
       <c r="E3" s="8">
-        <v>365990</v>
+        <v>388240</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="8">
-        <v>198312</v>
+        <v>193728</v>
       </c>
       <c r="C4" s="8">
-        <v>185136</v>
+        <v>175008</v>
       </c>
       <c r="D4" s="8">
-        <v>193540</v>
+        <v>185338</v>
       </c>
       <c r="E4" s="8">
-        <v>191023</v>
+        <v>186134</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="8">
-        <v>344436</v>
+        <v>368856</v>
       </c>
       <c r="C5" s="8">
-        <v>333036</v>
+        <v>333012</v>
       </c>
       <c r="D5" s="8">
-        <v>344519</v>
+        <v>351415</v>
       </c>
       <c r="E5" s="8">
-        <v>350111</v>
+        <v>352878</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="8">
-        <v>314808</v>
+        <v>306216</v>
       </c>
       <c r="C6" s="8">
-        <v>303096</v>
+        <v>299400</v>
       </c>
       <c r="D6" s="8">
-        <v>318155</v>
+        <v>313714</v>
       </c>
       <c r="E6" s="8">
-        <v>322329</v>
+        <v>316861</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8">
-        <v>299148</v>
+        <v>301788</v>
       </c>
       <c r="C7" s="8">
-        <v>272820</v>
+        <v>260400</v>
       </c>
       <c r="D7" s="8">
-        <v>287524</v>
+        <v>282859</v>
       </c>
       <c r="E7" s="8">
-        <v>284111</v>
+        <v>283634</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="7">
-        <v>1851060</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1759908</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1842470</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1850076</v>
+        <v>55</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1890120</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1754400</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1844468</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1857000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>54</v>
+      <c r="A10" s="10" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25"/>
@@ -1257,58 +1261,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
